--- a/data/trans_dic/IP16A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 53,33</t>
+          <t>15,34; 53,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,07; 52,56</t>
+          <t>21,46; 52,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 45,49</t>
+          <t>14,38; 45,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,54; 71,35</t>
+          <t>40,48; 71,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,18; 74,44</t>
+          <t>38,72; 72,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,2; 48,28</t>
+          <t>14,57; 47,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 46,6</t>
+          <t>17,32; 47,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,33; 77,3</t>
+          <t>42,31; 77,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,7; 59,39</t>
+          <t>33,66; 59,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,22; 45,64</t>
+          <t>23,4; 46,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,48; 40,22</t>
+          <t>17,54; 38,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,02; 70,47</t>
+          <t>47,48; 69,44</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,62; 59,04</t>
+          <t>23,99; 60,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,94; 56,02</t>
+          <t>25,62; 55,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 62,1</t>
+          <t>24,5; 62,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 63,89</t>
+          <t>29,73; 62,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,47; 63,44</t>
+          <t>23,45; 61,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,66; 68,77</t>
+          <t>23,69; 68,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,65; 63,22</t>
+          <t>29,12; 61,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,33; 63,71</t>
+          <t>27,73; 67,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,36; 54,03</t>
+          <t>28,88; 54,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,13; 56,12</t>
+          <t>30,27; 56,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,11; 57,45</t>
+          <t>31,94; 58,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,26; 59,4</t>
+          <t>34,82; 59,6</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,31; 67,96</t>
+          <t>19,17; 65,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,25; 72,9</t>
+          <t>34,94; 74,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 65,09</t>
+          <t>20,08; 64,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,66; 75,7</t>
+          <t>25,07; 76,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 50,09</t>
+          <t>18,44; 51,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,47; 81,19</t>
+          <t>41,34; 78,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,44; 76,96</t>
+          <t>31,67; 78,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 61,45</t>
+          <t>19,18; 59,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,0; 50,19</t>
+          <t>22,76; 49,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,32; 71,97</t>
+          <t>44,53; 71,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,3; 64,56</t>
+          <t>33,25; 66,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,7; 59,82</t>
+          <t>27,71; 58,25</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,24; 46,04</t>
+          <t>20,86; 47,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 49,45</t>
+          <t>28,14; 48,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,96; 52,76</t>
+          <t>30,89; 53,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 49,1</t>
+          <t>10,62; 50,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,2; 57,56</t>
+          <t>32,69; 57,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,96; 46,21</t>
+          <t>27,07; 46,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,03; 46,44</t>
+          <t>22,61; 46,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 51,98</t>
+          <t>27,75; 52,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,26; 48,25</t>
+          <t>30,98; 48,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,62; 44,32</t>
+          <t>29,54; 44,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,78; 46,9</t>
+          <t>30,8; 45,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,18; 45,55</t>
+          <t>18,2; 46,69</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 51,72</t>
+          <t>16,01; 51,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,41; 60,16</t>
+          <t>32,78; 60,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,64; 54,2</t>
+          <t>27,04; 54,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,47; 64,16</t>
+          <t>34,25; 65,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,8; 55,97</t>
+          <t>22,74; 55,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,67; 59,81</t>
+          <t>30,04; 58,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,54; 48,38</t>
+          <t>20,46; 48,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,49; 54,02</t>
+          <t>25,74; 53,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,22; 47,86</t>
+          <t>23,95; 47,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,16; 55,03</t>
+          <t>35,07; 55,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,81; 47,54</t>
+          <t>27,11; 46,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,8; 52,89</t>
+          <t>33,28; 54,07</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 66,98</t>
+          <t>8,66; 70,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,68; 89,0</t>
+          <t>47,41; 88,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,05; 47,54</t>
+          <t>8,21; 45,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,78; 68,87</t>
+          <t>23,4; 68,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,98; 52,99</t>
+          <t>11,14; 54,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,88; 49,41</t>
+          <t>9,73; 52,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,31; 60,07</t>
+          <t>15,87; 59,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,02; 65,36</t>
+          <t>21,09; 69,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 52,17</t>
+          <t>16,91; 49,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,05; 63,31</t>
+          <t>31,85; 63,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,31; 45,32</t>
+          <t>15,58; 43,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,59; 59,88</t>
+          <t>28,52; 60,69</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,72; 42,82</t>
+          <t>28,19; 43,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,26; 49,64</t>
+          <t>38,07; 49,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,81; 44,53</t>
+          <t>32,13; 44,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,09; 51,47</t>
+          <t>26,36; 50,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,14; 48,65</t>
+          <t>35,27; 49,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,35; 46,39</t>
+          <t>34,0; 46,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,08; 43,61</t>
+          <t>30,46; 43,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,48; 50,88</t>
+          <t>37,35; 50,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,55; 43,48</t>
+          <t>34,02; 44,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37,32; 45,92</t>
+          <t>37,68; 46,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,08; 42,09</t>
+          <t>33,1; 41,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,71; 48,67</t>
+          <t>32,57; 48,79</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9860</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5374</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14067</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12052</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>19182</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16863</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11723</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>33250</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2327; 8133</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5753; 14104</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2836; 8898</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10061; 17750</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8310; 15607</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3637; 11734</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3643; 10034</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>13287; 24203</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12332; 21934</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12113; 24226</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7147; 15678</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>26711; 39063</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7824</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10709</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8704</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11075</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>10126</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10901</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15208</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17659</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18830</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>21975</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4661; 11783</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6730; 14675</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4932; 12620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6966; 14603</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4188; 10972</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3530; 10196</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6482; 13736</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6514; 15782</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10770; 20140</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>12461; 23097</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13540; 24595</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>16339; 27968</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8520</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4957</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4820</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6493</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11955</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20450</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11499</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2130; 7249</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5577; 11893</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2386; 7702</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2406; 7298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4048; 11316</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7788; 14785</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3730; 9198</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3317; 10353</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7524; 16292</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15495; 24839</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7866; 15652</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7452; 15666</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12530</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23191</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23693</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21888</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17396</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26137</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14417</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22467</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>29927</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>49328</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38110</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>44355</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7860; 17710</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17020; 29291</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17473; 30056</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>8114; 38746</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12681; 22109</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>19695; 33606</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9722; 19908</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>15497; 29548</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>23689; 36916</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>39363; 58808</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>30660; 45440</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>24071; 61732</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5755</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17356</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14419</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14150</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9257</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15168</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9717</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>13981</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15012</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32523</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24136</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>28131</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3019; 9647</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12326; 22852</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9673; 19341</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9902; 18899</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5435; 13319</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10289; 20054</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6036; 14390</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9261; 19394</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10240; 20476</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>25193; 39545</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17700; 30257</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>21596; 35081</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8399</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5517</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4208</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>12597</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>11934</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>648; 5282</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5592; 10481</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1069; 5967</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2860; 8331</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1263; 6133</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1409; 7619</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1917; 7190</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3227; 10607</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3183; 9354</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>8367; 16745</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3913; 11007</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>7848; 16701</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>38208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>78036</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>60248</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>56671</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>71952</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>51359</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>79440</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>94879</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>149988</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>111608</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>150957</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>30935; 47371</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>68098; 89431</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>50470; 70347</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>46224; 89179</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>47721; 66525</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>61257; 83114</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>42541; 60887</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>66964; 91262</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>83353; 108287</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>135295; 166840</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>98233; 124305</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>115533; 173068</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,34; 53,61</t>
+          <t>15,44; 52,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,46; 52,62</t>
+          <t>21,76; 51,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,38; 45,11</t>
+          <t>12,44; 44,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,48; 71,42</t>
+          <t>40,03; 71,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,72; 72,72</t>
+          <t>36,96; 72,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,57; 47,02</t>
+          <t>16,33; 47,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,32; 47,72</t>
+          <t>17,05; 50,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,31; 77,08</t>
+          <t>44,55; 76,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,66; 59,88</t>
+          <t>33,08; 59,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,4; 46,81</t>
+          <t>24,13; 45,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 38,47</t>
+          <t>17,95; 41,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,48; 69,44</t>
+          <t>47,2; 71,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,99; 60,64</t>
+          <t>23,18; 59,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,62; 55,88</t>
+          <t>25,25; 57,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,5; 62,69</t>
+          <t>25,52; 61,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,73; 62,32</t>
+          <t>31,26; 65,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,45; 61,44</t>
+          <t>25,33; 62,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 68,43</t>
+          <t>24,29; 66,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,12; 61,7</t>
+          <t>27,55; 63,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,73; 67,18</t>
+          <t>28,22; 65,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,88; 54,01</t>
+          <t>28,3; 53,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,27; 56,11</t>
+          <t>31,64; 56,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,94; 58,02</t>
+          <t>33,3; 58,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,82; 59,6</t>
+          <t>35,01; 59,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 65,25</t>
+          <t>21,62; 67,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,94; 74,51</t>
+          <t>35,13; 74,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,08; 64,81</t>
+          <t>21,33; 65,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,07; 76,06</t>
+          <t>24,52; 75,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,44; 51,55</t>
+          <t>18,65; 52,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,34; 78,49</t>
+          <t>44,52; 81,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,67; 78,1</t>
+          <t>32,01; 79,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,18; 59,85</t>
+          <t>20,23; 62,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,76; 49,28</t>
+          <t>22,44; 49,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,53; 71,38</t>
+          <t>43,43; 70,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,25; 66,15</t>
+          <t>32,78; 66,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,71; 58,25</t>
+          <t>26,78; 60,57</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,86; 47,0</t>
+          <t>20,79; 45,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,14; 48,43</t>
+          <t>28,63; 48,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,89; 53,14</t>
+          <t>31,35; 52,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 50,73</t>
+          <t>10,7; 49,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,69; 57,0</t>
+          <t>32,37; 58,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,07; 46,19</t>
+          <t>27,1; 46,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,61; 46,3</t>
+          <t>23,39; 46,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,75; 52,91</t>
+          <t>27,96; 52,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,98; 48,27</t>
+          <t>30,72; 48,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,54; 44,14</t>
+          <t>30,49; 44,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,8; 45,64</t>
+          <t>30,53; 46,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 46,69</t>
+          <t>16,8; 45,36</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 51,17</t>
+          <t>14,62; 49,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,78; 60,78</t>
+          <t>32,81; 58,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,04; 54,06</t>
+          <t>27,09; 53,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,25; 65,38</t>
+          <t>34,2; 64,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 55,73</t>
+          <t>23,79; 55,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,04; 58,56</t>
+          <t>30,56; 58,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 48,77</t>
+          <t>20,18; 48,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,74; 53,91</t>
+          <t>26,08; 53,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,95; 47,89</t>
+          <t>23,36; 47,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,07; 55,04</t>
+          <t>34,8; 55,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,11; 46,35</t>
+          <t>26,95; 46,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,28; 54,07</t>
+          <t>32,47; 53,1</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,66; 70,57</t>
+          <t>8,64; 62,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,41; 88,86</t>
+          <t>47,09; 89,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,21; 45,81</t>
+          <t>8,97; 45,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,4; 68,17</t>
+          <t>22,46; 65,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 54,1</t>
+          <t>11,58; 55,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,73; 52,63</t>
+          <t>10,23; 48,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,87; 59,49</t>
+          <t>15,27; 60,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,09; 69,33</t>
+          <t>21,62; 66,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,91; 49,7</t>
+          <t>14,31; 49,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,85; 63,74</t>
+          <t>32,06; 63,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,58; 43,83</t>
+          <t>16,05; 46,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28,52; 60,69</t>
+          <t>27,12; 61,62</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,19; 43,17</t>
+          <t>28,54; 42,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,07; 49,99</t>
+          <t>37,45; 49,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,13; 44,78</t>
+          <t>32,42; 44,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,36; 50,85</t>
+          <t>22,35; 51,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,27; 49,17</t>
+          <t>35,3; 49,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,0; 46,13</t>
+          <t>34,47; 46,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,46; 43,6</t>
+          <t>29,83; 43,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,35; 50,9</t>
+          <t>38,03; 50,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>34,02; 44,19</t>
+          <t>33,27; 43,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37,68; 46,46</t>
+          <t>37,62; 46,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,1; 41,89</t>
+          <t>33,15; 42,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,57; 48,79</t>
+          <t>32,17; 48,6</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2327; 8133</t>
+          <t>2342; 8002</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5753; 14104</t>
+          <t>5832; 13862</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2836; 8898</t>
+          <t>2454; 8765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10061; 17750</t>
+          <t>9948; 17806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8310; 15607</t>
+          <t>7933; 15460</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3637; 11734</t>
+          <t>4076; 11877</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3643; 10034</t>
+          <t>3586; 10549</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13287; 24203</t>
+          <t>13991; 24040</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12332; 21934</t>
+          <t>12117; 21658</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12113; 24226</t>
+          <t>12491; 23423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7147; 15678</t>
+          <t>7314; 16759</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26711; 39063</t>
+          <t>26554; 40327</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4661; 11783</t>
+          <t>4504; 11527</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6730; 14675</t>
+          <t>6631; 15007</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4932; 12620</t>
+          <t>5138; 12463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6966; 14603</t>
+          <t>7326; 15285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4188; 10972</t>
+          <t>4524; 11143</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3530; 10196</t>
+          <t>3620; 9920</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6482; 13736</t>
+          <t>6132; 14155</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6514; 15782</t>
+          <t>6630; 15354</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10770; 20140</t>
+          <t>10553; 19979</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12461; 23097</t>
+          <t>13025; 23148</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13540; 24595</t>
+          <t>14118; 24692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16339; 27968</t>
+          <t>16426; 27992</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2130; 7249</t>
+          <t>2402; 7461</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5577; 11893</t>
+          <t>5606; 11863</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2386; 7702</t>
+          <t>2534; 7828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2406; 7298</t>
+          <t>2353; 7268</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4048; 11316</t>
+          <t>4094; 11554</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7788; 14785</t>
+          <t>8387; 15272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3730; 9198</t>
+          <t>3771; 9385</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3317; 10353</t>
+          <t>3498; 10798</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7524; 16292</t>
+          <t>7421; 16509</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15495; 24839</t>
+          <t>15115; 24698</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7866; 15652</t>
+          <t>7757; 15668</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7452; 15666</t>
+          <t>7202; 16290</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7860; 17710</t>
+          <t>7836; 17287</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17020; 29291</t>
+          <t>17317; 29472</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17473; 30056</t>
+          <t>17734; 29505</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8114; 38746</t>
+          <t>8174; 37904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12681; 22109</t>
+          <t>12555; 22703</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19695; 33606</t>
+          <t>19718; 33693</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9722; 19908</t>
+          <t>10059; 19916</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15497; 29548</t>
+          <t>15613; 29088</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23689; 36916</t>
+          <t>23491; 37399</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39363; 58808</t>
+          <t>40621; 59498</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30660; 45440</t>
+          <t>30397; 46071</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24071; 61732</t>
+          <t>22215; 59975</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3019; 9647</t>
+          <t>2757; 9260</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12326; 22852</t>
+          <t>12336; 22137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9673; 19341</t>
+          <t>9693; 19197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9902; 18899</t>
+          <t>9887; 18531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5435; 13319</t>
+          <t>5686; 13302</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10289; 20054</t>
+          <t>10464; 20040</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6036; 14390</t>
+          <t>5955; 14347</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9261; 19394</t>
+          <t>9383; 19319</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10240; 20476</t>
+          <t>9986; 20448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25193; 39545</t>
+          <t>24999; 39733</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17700; 30257</t>
+          <t>17596; 30616</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21596; 35081</t>
+          <t>21069; 34451</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>648; 5282</t>
+          <t>646; 4710</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5592; 10481</t>
+          <t>5554; 10515</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1069; 5967</t>
+          <t>1168; 5961</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2860; 8331</t>
+          <t>2745; 8038</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1263; 6133</t>
+          <t>1313; 6320</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1409; 7619</t>
+          <t>1481; 7067</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1917; 7190</t>
+          <t>1846; 7306</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3227; 10607</t>
+          <t>3308; 10215</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3183; 9354</t>
+          <t>2693; 9360</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8367; 16745</t>
+          <t>8424; 16724</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3913; 11007</t>
+          <t>4031; 11779</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7848; 16701</t>
+          <t>7464; 16958</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30935; 47371</t>
+          <t>31314; 46600</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>68098; 89431</t>
+          <t>67006; 88573</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50470; 70347</t>
+          <t>50937; 70321</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46224; 89179</t>
+          <t>39191; 90404</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47721; 66525</t>
+          <t>47760; 66810</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61257; 83114</t>
+          <t>62097; 83211</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42541; 60887</t>
+          <t>41660; 61269</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>66964; 91262</t>
+          <t>68193; 91023</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>83353; 108287</t>
+          <t>81515; 106643</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>135295; 166840</t>
+          <t>135082; 167204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98233; 124305</t>
+          <t>98371; 126513</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>115533; 173068</t>
+          <t>114118; 172392</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A02-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56,15%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30,19%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61,37%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>36,79%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>27,25%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>56,15%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,19%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,44; 52,74</t>
+          <t>40,18; 74,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,76; 51,72</t>
+          <t>16,2; 48,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,44; 44,44</t>
+          <t>14,94; 46,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,03; 71,65</t>
+          <t>44,05; 78,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,96; 72,03</t>
+          <t>14,48; 53,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 47,6</t>
+          <t>22,07; 52,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 50,17</t>
+          <t>14,33; 45,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,55; 76,56</t>
+          <t>40,22; 71,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,08; 59,12</t>
+          <t>33,7; 59,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,13; 45,26</t>
+          <t>23,22; 45,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,95; 41,12</t>
+          <t>18,48; 40,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,2; 71,69</t>
+          <t>47,55; 70,59</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46,57%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>40,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>40,78%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>43,24%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47,26%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>46,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,18; 59,33</t>
+          <t>24,47; 63,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,25; 57,14</t>
+          <t>26,66; 68,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,52; 61,91</t>
+          <t>29,65; 63,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,26; 65,23</t>
+          <t>27,12; 63,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,33; 62,4</t>
+          <t>23,62; 59,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,29; 66,57</t>
+          <t>24,94; 56,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,55; 63,59</t>
+          <t>25,71; 62,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,22; 65,36</t>
+          <t>31,03; 64,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,3; 53,58</t>
+          <t>27,36; 54,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,64; 56,23</t>
+          <t>31,13; 56,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,3; 58,25</t>
+          <t>32,11; 57,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,01; 59,65</t>
+          <t>35,56; 60,13</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,14%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63,33%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39,36%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>42,13%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>53,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>41,72%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>50,23%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>55,54%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,62; 67,16</t>
+          <t>18,19; 50,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,13; 74,32</t>
+          <t>42,47; 81,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,33; 65,87</t>
+          <t>31,44; 76,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,52; 75,74</t>
+          <t>19,8; 62,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 52,63</t>
+          <t>21,31; 67,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,52; 81,07</t>
+          <t>33,25; 72,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,01; 79,68</t>
+          <t>18,04; 65,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,23; 62,43</t>
+          <t>29,41; 79,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,44; 49,93</t>
+          <t>24,0; 50,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,43; 70,97</t>
+          <t>44,32; 71,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,78; 66,22</t>
+          <t>31,3; 64,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,78; 60,57</t>
+          <t>29,34; 61,77</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37,66%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>33,25%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>41,89%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28,66%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,53%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,79; 45,87</t>
+          <t>33,2; 57,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,63; 48,73</t>
+          <t>26,96; 46,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,35; 52,17</t>
+          <t>22,03; 46,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 49,62</t>
+          <t>24,99; 49,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,37; 58,53</t>
+          <t>21,24; 46,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,1; 46,31</t>
+          <t>29,2; 49,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 46,32</t>
+          <t>31,96; 52,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,96; 52,09</t>
+          <t>33,08; 58,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,72; 48,9</t>
+          <t>30,26; 48,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,49; 44,66</t>
+          <t>30,62; 44,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,53; 46,28</t>
+          <t>30,78; 46,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,8; 45,36</t>
+          <t>32,22; 50,19</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38,73%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>44,29%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32,93%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40,33%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>30,53%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>46,16%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>40,3%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>38,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>44,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 49,12</t>
+          <t>24,8; 55,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,81; 58,88</t>
+          <t>31,67; 59,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,09; 53,65</t>
+          <t>20,54; 48,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,2; 64,11</t>
+          <t>25,7; 56,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 55,66</t>
+          <t>15,56; 51,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,56; 58,52</t>
+          <t>32,41; 60,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,18; 48,63</t>
+          <t>28,64; 54,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,08; 53,7</t>
+          <t>33,58; 64,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,36; 47,83</t>
+          <t>23,22; 47,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,8; 55,3</t>
+          <t>36,16; 55,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,95; 46,9</t>
+          <t>27,81; 47,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,47; 53,1</t>
+          <t>33,76; 53,95</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>34,82%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43,62%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>34,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>71,21%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23,81%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,82%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 62,93</t>
+          <t>10,98; 52,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,09; 89,15</t>
+          <t>9,88; 49,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,97; 45,77</t>
+          <t>15,31; 60,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,46; 65,77</t>
+          <t>20,43; 66,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,58; 55,75</t>
+          <t>8,56; 66,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,23; 48,82</t>
+          <t>46,68; 89,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,27; 60,45</t>
+          <t>9,05; 47,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 66,77</t>
+          <t>20,92; 70,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,31; 49,73</t>
+          <t>14,2; 52,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,06; 63,66</t>
+          <t>31,05; 63,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,05; 46,91</t>
+          <t>16,31; 45,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,12; 61,62</t>
+          <t>28,58; 61,2</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41,89%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39,94%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36,78%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>34,82%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>43,62%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>38,35%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>40,78%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>41,89%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,78%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,54; 42,47</t>
+          <t>35,14; 48,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,45; 49,51</t>
+          <t>34,35; 46,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,42; 44,76</t>
+          <t>30,08; 43,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,35; 51,55</t>
+          <t>37,27; 51,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,3; 49,38</t>
+          <t>27,72; 42,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,47; 46,19</t>
+          <t>37,26; 49,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,83; 43,87</t>
+          <t>32,81; 44,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,03; 50,76</t>
+          <t>42,51; 57,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,27; 43,52</t>
+          <t>33,55; 43,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37,62; 46,57</t>
+          <t>37,32; 45,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,15; 42,63</t>
+          <t>33,08; 42,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,17; 48,6</t>
+          <t>41,73; 51,59</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12052</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17700</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4811</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9860</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5374</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14067</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12052</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7570</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33250</t>
+          <t>31578</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2342; 8002</t>
+          <t>8624; 15977</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5832; 13862</t>
+          <t>4043; 12047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2454; 8765</t>
+          <t>3141; 9799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9948; 17806</t>
+          <t>12705; 22603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7933; 15460</t>
+          <t>2196; 8090</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4076; 11877</t>
+          <t>5917; 14087</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3586; 10549</t>
+          <t>2825; 8972</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13991; 24040</t>
+          <t>9909; 17547</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12117; 21658</t>
+          <t>12345; 21756</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12491; 23423</t>
+          <t>12019; 23622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7314; 16759</t>
+          <t>7533; 16389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26554; 40327</t>
+          <t>25429; 37749</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10126</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10538</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7824</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10709</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8704</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11075</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7383</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6949</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10126</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21665</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4504; 11527</t>
+          <t>4369; 11329</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6631; 15007</t>
+          <t>3973; 10247</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5138; 12463</t>
+          <t>6600; 14073</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7326; 15285</t>
+          <t>6135; 14432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4524; 11143</t>
+          <t>4588; 11471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3620; 9920</t>
+          <t>6550; 14713</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6132; 14155</t>
+          <t>5175; 12501</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6630; 15354</t>
+          <t>7130; 14842</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10553; 19979</t>
+          <t>10202; 20146</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13025; 23148</t>
+          <t>12815; 23101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14118; 24692</t>
+          <t>13613; 24352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16426; 27992</t>
+          <t>16216; 27420</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5914</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4680</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8520</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4957</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4820</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7275</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11929</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6542</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11009</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2402; 7461</t>
+          <t>3993; 10996</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5606; 11863</t>
+          <t>8000; 15295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2534; 7828</t>
+          <t>3703; 9064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2353; 7268</t>
+          <t>2974; 9441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4094; 11554</t>
+          <t>2368; 7551</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8387; 15272</t>
+          <t>5307; 11636</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3771; 9385</t>
+          <t>2144; 7735</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3498; 10798</t>
+          <t>2799; 7521</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7421; 16509</t>
+          <t>7934; 16595</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15115; 24698</t>
+          <t>15423; 25045</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7757; 15668</t>
+          <t>7405; 15276</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7202; 16290</t>
+          <t>7202; 15160</t>
         </is>
       </c>
     </row>
@@ -2415,37 +2415,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17396</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26137</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14417</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18734</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>12530</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>23191</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23693</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21888</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17396</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26137</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14417</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>38506</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7836; 17287</t>
+          <t>12880; 22325</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17317; 29472</t>
+          <t>19613; 33622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17734; 29505</t>
+          <t>9474; 19969</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8174; 37904</t>
+          <t>12432; 24595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12555; 22703</t>
+          <t>8005; 17349</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19718; 33693</t>
+          <t>17658; 29906</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10059; 19916</t>
+          <t>18076; 29842</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15613; 29088</t>
+          <t>14072; 24732</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23491; 37399</t>
+          <t>23140; 36902</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40621; 59498</t>
+          <t>40793; 59042</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30397; 46071</t>
+          <t>30645; 46691</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22215; 59975</t>
+          <t>29738; 46318</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>9257</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15168</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9717</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12975</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5755</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>17356</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>14419</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14150</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>9257</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15168</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9717</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>27065</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2757; 9260</t>
+          <t>5926; 13376</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12336; 22137</t>
+          <t>10846; 20482</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9693; 19197</t>
+          <t>6059; 14273</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9887; 18531</t>
+          <t>8267; 18069</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5686; 13302</t>
+          <t>2933; 9751</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10464; 20040</t>
+          <t>12187; 22619</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5955; 14347</t>
+          <t>10246; 19393</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9383; 19319</t>
+          <t>9607; 18507</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9986; 20448</t>
+          <t>9929; 20459</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24999; 39733</t>
+          <t>25980; 39538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17596; 30616</t>
+          <t>18155; 31038</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21069; 34451</t>
+          <t>20521; 32793</t>
         </is>
       </c>
     </row>
@@ -2831,37 +2831,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4208</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6157</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2606</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>8399</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3101</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5517</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3307</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4198</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>11839</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>646; 4710</t>
+          <t>1245; 6007</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5554; 10515</t>
+          <t>1430; 7152</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1168; 5961</t>
+          <t>1851; 7260</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2745; 8038</t>
+          <t>2883; 9383</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1313; 6320</t>
+          <t>641; 5013</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1481; 7067</t>
+          <t>5506; 10498</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1846; 7306</t>
+          <t>1179; 6193</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3308; 10215</t>
+          <t>2604; 8735</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2693; 9360</t>
+          <t>2673; 9818</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8424; 16724</t>
+          <t>8157; 16632</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4031; 11779</t>
+          <t>4095; 11379</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7464; 16958</t>
+          <t>7591; 16258</t>
         </is>
       </c>
     </row>
@@ -3039,37 +3039,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>56671</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>71952</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>51359</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>72018</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>38208</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>78036</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>56671</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>71952</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>51359</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>79440</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>150957</t>
+          <t>141662</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31314; 46600</t>
+          <t>47548; 65817</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>67006; 88573</t>
+          <t>61891; 83578</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50937; 70321</t>
+          <t>42007; 60906</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39191; 90404</t>
+          <t>60575; 83394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47760; 66810</t>
+          <t>30418; 46985</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62097; 83211</t>
+          <t>66652; 88809</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41660; 61269</t>
+          <t>51546; 69950</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>68193; 91023</t>
+          <t>59821; 80432</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>81515; 106643</t>
+          <t>82199; 106550</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>135082; 167204</t>
+          <t>134019; 164889</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98371; 126513</t>
+          <t>98153; 124903</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>114118; 172392</t>
+          <t>126541; 156448</t>
         </is>
       </c>
     </row>
